--- a/Projetos/Lojas Conamore/Relatórios Pagar.me/ACL/Pagarme_ACL_2026-06-21.xlsx
+++ b/Projetos/Lojas Conamore/Relatórios Pagar.me/ACL/Pagarme_ACL_2026-06-21.xlsx
@@ -542,12 +542,12 @@
           <t>6M4GWU5SQ8</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>6M4GWU5SQ8</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="2" t="n">
         <v>395.6</v>
       </c>
       <c r="G2" t="inlineStr">
@@ -612,12 +612,12 @@
           <t>04E3CWF928</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>04E3CWF928</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="2" t="n">
         <v>157.51</v>
       </c>
       <c r="G3" t="inlineStr">
@@ -682,12 +682,12 @@
           <t>5O51TYJTEW</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>11000029931</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="2" t="n">
         <v>176.33</v>
       </c>
       <c r="G4" t="inlineStr">
@@ -744,12 +744,12 @@
           <t>8XZ9TY1ULP</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>44000002483</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="2" t="n">
         <v>224.2</v>
       </c>
       <c r="G5" t="inlineStr">
@@ -806,12 +806,12 @@
           <t>EL1MHJMIVW</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>44000002484</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="2" t="n">
         <v>262.86</v>
       </c>
       <c r="G6" t="inlineStr">
@@ -868,12 +868,12 @@
           <t>40Z5AKGAJ4</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>11000029932</t>
         </is>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="2" t="n">
         <v>338.88</v>
       </c>
       <c r="G7" t="inlineStr">
@@ -930,12 +930,12 @@
           <t>6O8OA12SRK</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>6O8OA12SRK</t>
         </is>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="2" t="n">
         <v>511.18</v>
       </c>
       <c r="G8" t="inlineStr">
@@ -1000,12 +1000,12 @@
           <t>91DYC2WTX5</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>11000029935</t>
         </is>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="2" t="n">
         <v>344.44</v>
       </c>
       <c r="G9" t="inlineStr">
@@ -1062,12 +1062,12 @@
           <t>P9QSX5H85P</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>11000029936</t>
         </is>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="2" t="n">
         <v>174.49</v>
       </c>
       <c r="G10" t="inlineStr">
@@ -1124,12 +1124,12 @@
           <t>N909HY6B8G</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>11000029938</t>
         </is>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="2" t="n">
         <v>1136.06</v>
       </c>
       <c r="G11" t="inlineStr">
@@ -1186,12 +1186,12 @@
           <t>XJJRAZJU06</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>11000029940</t>
         </is>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="2" t="n">
         <v>264.52</v>
       </c>
       <c r="G12" t="inlineStr">
@@ -1248,12 +1248,12 @@
           <t>P69QB6CEKP</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>P69QB6CEKP</t>
         </is>
       </c>
-      <c r="F13" t="n">
+      <c r="F13" s="2" t="n">
         <v>1457.4</v>
       </c>
       <c r="G13" t="inlineStr">
@@ -1318,12 +1318,12 @@
           <t>LK17C24U2E</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>LK17C24U2E</t>
         </is>
       </c>
-      <c r="F14" t="n">
+      <c r="F14" s="2" t="n">
         <v>1546.3</v>
       </c>
       <c r="G14" t="inlineStr">
@@ -1388,12 +1388,12 @@
           <t>6KNOC9KBE6</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>11000029943</t>
         </is>
       </c>
-      <c r="F15" t="n">
+      <c r="F15" s="2" t="n">
         <v>430.86</v>
       </c>
       <c r="G15" t="inlineStr">
@@ -1450,12 +1450,12 @@
           <t>Q6O1I1LU95</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Q6O1I1LU95</t>
         </is>
       </c>
-      <c r="F16" t="n">
+      <c r="F16" s="2" t="n">
         <v>313.4</v>
       </c>
       <c r="G16" t="inlineStr">
@@ -1520,12 +1520,12 @@
           <t>JD1ZIZIY3P</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>JD1ZIZIY3P</t>
         </is>
       </c>
-      <c r="F17" t="n">
+      <c r="F17" s="2" t="n">
         <v>408.5</v>
       </c>
       <c r="G17" t="inlineStr">
@@ -1590,12 +1590,12 @@
           <t>L5EDB6HY5G</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>L5EDB6HY5G</t>
         </is>
       </c>
-      <c r="F18" t="n">
+      <c r="F18" s="2" t="n">
         <v>148.22</v>
       </c>
       <c r="G18" t="inlineStr">
